--- a/public/assets/templates/maintenance/sipil.xlsx
+++ b/public/assets/templates/maintenance/sipil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0010A5-E3E0-42F0-BC4C-69A88F757FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5F7860-20D9-4A53-A4CE-0792F7001291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{CED63628-A031-421C-BEDE-C7C97718D329}"/>
   </bookViews>
@@ -597,9 +597,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -618,6 +615,129 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -639,140 +759,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1157,252 +1157,252 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="21" customHeight="1" thickTop="1">
-      <c r="A1" s="50"/>
-      <c r="B1" s="51"/>
-      <c r="C1" s="15" t="s">
+      <c r="A1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="16"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="56"/>
     </row>
     <row r="2" spans="1:9" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="17" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9" customFormat="1" ht="16" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="19" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="59"/>
+      <c r="G3" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="21"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="61"/>
     </row>
     <row r="4" spans="1:9" customFormat="1" ht="16" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="61"/>
     </row>
     <row r="5" spans="1:9" customFormat="1" ht="13" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="55" t="s">
+      <c r="E5" s="54"/>
+      <c r="F5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="56"/>
-    </row>
-    <row r="6" spans="1:9" s="12" customFormat="1" ht="13" customHeight="1">
-      <c r="A6" s="54"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" s="11" customFormat="1" ht="13" customHeight="1">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="56"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="21"/>
     </row>
     <row r="7" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="64"/>
     </row>
     <row r="8" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="49"/>
+      <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="64"/>
     </row>
     <row r="9" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="49"/>
+      <c r="C9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="26"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="64"/>
     </row>
     <row r="10" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="49"/>
+      <c r="C10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="26"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="64"/>
     </row>
     <row r="11" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="49"/>
+      <c r="C11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="26"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="64"/>
     </row>
     <row r="12" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="49"/>
+      <c r="C12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="26"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="64"/>
     </row>
     <row r="13" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="51"/>
+      <c r="C13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="26"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="64"/>
     </row>
     <row r="14" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="29"/>
+      <c r="A14" s="52"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="66"/>
     </row>
     <row r="15" spans="1:9" s="7" customFormat="1" ht="60" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="32"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="44"/>
     </row>
     <row r="16" spans="1:9" customFormat="1">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="33" t="s">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="47"/>
     </row>
     <row r="17" spans="1:9" customFormat="1" ht="12" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="36" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="36"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="6" t="s">
         <v>9</v>
       </c>
@@ -1414,247 +1414,247 @@
       </c>
     </row>
     <row r="18" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="59"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="59"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="59"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="59"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="59"/>
-      <c r="B24" s="60"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="60"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="59"/>
-      <c r="B25" s="60"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="59"/>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="59"/>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="59"/>
-      <c r="B28" s="60"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="59"/>
-      <c r="B29" s="60"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="59"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="59"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="59"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A33" s="59"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="60"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="46" t="s">
+      <c r="A33" s="26"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="46"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="43"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A34" s="59"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="48" t="s">
+      <c r="A34" s="26"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="48"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="58"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="25"/>
     </row>
     <row r="35" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A35" s="59"/>
-      <c r="B35" s="60"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="60"/>
-      <c r="E35" s="63" t="s">
+      <c r="A35" s="26"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="63"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="43"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A36" s="59"/>
-      <c r="B36" s="60"/>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="48" t="s">
+      <c r="A36" s="26"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="25"/>
     </row>
     <row r="37" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A37" s="59"/>
-      <c r="B37" s="60"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="60"/>
-      <c r="E37" s="63" t="s">
+      <c r="A37" s="26"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="63"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="43"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="23"/>
     </row>
     <row r="38" spans="1:9" customFormat="1" ht="11" customHeight="1" thickBot="1">
-      <c r="A38" s="61"/>
-      <c r="B38" s="62"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="65" t="s">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="65"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="45"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="38"/>
     </row>
     <row r="39" spans="1:9" customFormat="1" ht="12" customHeight="1" thickTop="1">
       <c r="A39" s="1"/>
@@ -1663,11 +1663,11 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="41" t="s">
+      <c r="G39" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
     </row>
     <row r="40" spans="1:9" customFormat="1" ht="9" customHeight="1"/>
     <row r="41" spans="1:9" customFormat="1"/>
@@ -1679,38 +1679,18 @@
     <row r="47" spans="1:9" customFormat="1"/>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="F5:I6"/>
-    <mergeCell ref="H33:I34"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="A16:D38"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="H37:I38"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C5:C6"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="F9:I9"/>
@@ -1723,18 +1703,38 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="F5:I6"/>
+    <mergeCell ref="H33:I34"/>
+    <mergeCell ref="H35:I36"/>
+    <mergeCell ref="A16:D38"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.196527777777778" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/sipil.xlsx
+++ b/public/assets/templates/maintenance/sipil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5F7860-20D9-4A53-A4CE-0792F7001291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ACE5F5-96DB-4928-B4CF-1C088DCF39C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{CED63628-A031-421C-BEDE-C7C97718D329}"/>
   </bookViews>
@@ -615,6 +615,114 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -630,148 +738,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1157,30 +1157,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="21" customHeight="1" thickTop="1">
-      <c r="A1" s="14"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="55" t="s">
+      <c r="A1" s="50"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="57" t="s">
+      <c r="A2" s="52"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="58"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18"/>
     </row>
     <row r="3" spans="1:9" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="13" t="s">
@@ -1191,15 +1191,15 @@
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="59"/>
-      <c r="G3" s="60" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="I3" s="61"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:9" customFormat="1" ht="16" customHeight="1">
       <c r="A4" s="13" t="s">
@@ -1210,199 +1210,199 @@
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="61"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="21"/>
     </row>
     <row r="5" spans="1:9" customFormat="1" ht="13" customHeight="1">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
     </row>
     <row r="6" spans="1:9" s="11" customFormat="1" ht="13" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
       <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="21"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="56"/>
     </row>
     <row r="7" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="49"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="64"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="49"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="64"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="49"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="64"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="49"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="10"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="64"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="49"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="64"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="49"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="10"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="64"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="51"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="10"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="64"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="26"/>
     </row>
     <row r="14" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="53"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="9"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="66"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
     </row>
     <row r="15" spans="1:9" s="7" customFormat="1" ht="60" customHeight="1">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
     </row>
     <row r="16" spans="1:9" customFormat="1">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="45" t="s">
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
     </row>
     <row r="17" spans="1:9" customFormat="1" ht="12" customHeight="1">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="39" t="s">
+      <c r="A17" s="63"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="39"/>
+      <c r="F17" s="34"/>
       <c r="G17" s="6" t="s">
         <v>9</v>
       </c>
@@ -1414,247 +1414,247 @@
       </c>
     </row>
     <row r="18" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
+      <c r="A18" s="63"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
+      <c r="A19" s="63"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
+      <c r="A20" s="63"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
+      <c r="A21" s="63"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
+      <c r="A22" s="63"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
+      <c r="A24" s="63"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="A25" s="63"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
+      <c r="A26" s="63"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
+      <c r="A27" s="63"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="26"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
+      <c r="A28" s="63"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="26"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="26"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
+      <c r="A30" s="63"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="26"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
+      <c r="A31" s="63"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="26"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
+      <c r="A32" s="63"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A33" s="26"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="40" t="s">
+      <c r="A33" s="63"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="23"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="43"/>
     </row>
     <row r="34" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A34" s="26"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="32" t="s">
+      <c r="A34" s="63"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="32"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="25"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="58"/>
     </row>
     <row r="35" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A35" s="26"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="30" t="s">
+      <c r="A35" s="63"/>
+      <c r="B35" s="64"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="23"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A36" s="26"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="32" t="s">
+      <c r="A36" s="63"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="F36" s="32"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="25"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="58"/>
     </row>
     <row r="37" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A37" s="26"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="30" t="s">
+      <c r="A37" s="63"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="30"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="23"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="43"/>
     </row>
     <row r="38" spans="1:9" customFormat="1" ht="11" customHeight="1" thickBot="1">
-      <c r="A38" s="28"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="34" t="s">
+      <c r="A38" s="65"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="34"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="38"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="45"/>
     </row>
     <row r="39" spans="1:9" customFormat="1" ht="12" customHeight="1" thickTop="1">
       <c r="A39" s="1"/>
@@ -1663,11 +1663,11 @@
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="36" t="s">
+      <c r="G39" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41"/>
     </row>
     <row r="40" spans="1:9" customFormat="1" ht="9" customHeight="1"/>
     <row r="41" spans="1:9" customFormat="1"/>
@@ -1679,46 +1679,6 @@
     <row r="47" spans="1:9" customFormat="1"/>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="H37:I38"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E34:G34"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A5:B6"/>
     <mergeCell ref="F5:I6"/>
@@ -1735,6 +1695,46 @@
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="H37:I38"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="E16:I16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.196527777777778" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/sipil.xlsx
+++ b/public/assets/templates/maintenance/sipil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2ACE5F5-96DB-4928-B4CF-1C088DCF39C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57968CF9-0D57-47A2-80F0-4E4ACADF37C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{CED63628-A031-421C-BEDE-C7C97718D329}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>FRM/EUT/01/009/019-01</t>
   </si>
@@ -129,9 +129,6 @@
     <t>:</t>
   </si>
   <si>
-    <t xml:space="preserve">Waktu   </t>
-  </si>
-  <si>
     <t>Area</t>
   </si>
   <si>
@@ -142,6 +139,21 @@
   </si>
   <si>
     <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Waktu Mulai</t>
+  </si>
+  <si>
+    <t>Waktu Selesai</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
+  </si>
+  <si>
+    <t>Departemen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">: </t>
   </si>
 </sst>
 </file>
@@ -572,7 +584,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -618,6 +630,141 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -639,140 +786,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1141,14 +1159,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1270B244-2998-4EEB-BD29-B19C96E8EA80}">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="3" style="1" customWidth="1"/>
     <col min="3" max="3" width="23" style="1" customWidth="1"/>
-    <col min="4" max="5" width="5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="2.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.26953125" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.90625" style="1" customWidth="1"/>
     <col min="8" max="8" width="4.7265625" style="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="1" customWidth="1"/>
@@ -1157,563 +1176,569 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="21" customHeight="1" thickTop="1">
-      <c r="A1" s="50"/>
-      <c r="B1" s="51"/>
-      <c r="C1" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="16"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="61"/>
     </row>
     <row r="2" spans="1:9" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="63"/>
     </row>
     <row r="3" spans="1:9" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20" t="s">
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="21"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
     </row>
     <row r="4" spans="1:9" customFormat="1" ht="16" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
-    </row>
-    <row r="5" spans="1:9" customFormat="1" ht="13" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="64"/>
+      <c r="G4" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="65"/>
+      <c r="I4" s="66"/>
+    </row>
+    <row r="5" spans="1:9" customFormat="1" ht="16" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="64"/>
+      <c r="G5" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="65"/>
+      <c r="I5" s="66"/>
+    </row>
+    <row r="6" spans="1:9" customFormat="1" ht="13" customHeight="1">
+      <c r="A6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D6" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="55" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="56"/>
-    </row>
-    <row r="6" spans="1:9" s="11" customFormat="1" ht="13" customHeight="1">
-      <c r="A6" s="54"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" spans="1:9" s="11" customFormat="1" ht="13" customHeight="1">
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="56"/>
-    </row>
-    <row r="7" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
+      <c r="A8" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="9" t="s">
+      <c r="B8" s="52"/>
+      <c r="C8" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26"/>
-    </row>
-    <row r="8" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="54"/>
     </row>
     <row r="9" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A9" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="24"/>
+      <c r="A9" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="52"/>
       <c r="C9" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="14"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="26"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="54"/>
     </row>
     <row r="10" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="24"/>
+      <c r="A10" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="52"/>
       <c r="C10" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="14"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="26"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="54"/>
     </row>
     <row r="11" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A11" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="24"/>
+      <c r="A11" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="52"/>
       <c r="C11" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="26"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="54"/>
     </row>
     <row r="12" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A12" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="24"/>
+      <c r="A12" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="52"/>
       <c r="C12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="14"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="26"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="54"/>
     </row>
     <row r="13" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A13" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="31"/>
+      <c r="A13" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="52"/>
       <c r="C13" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="26"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="54"/>
     </row>
     <row r="14" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="8"/>
+      <c r="A14" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="56"/>
+      <c r="C14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="10"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="29"/>
-    </row>
-    <row r="15" spans="1:9" s="7" customFormat="1" ht="60" customHeight="1">
-      <c r="A15" s="35" t="s">
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="54"/>
+    </row>
+    <row r="15" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
+      <c r="A15" s="57"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="50"/>
+    </row>
+    <row r="16" spans="1:9" s="7" customFormat="1" ht="60" customHeight="1">
+      <c r="A16" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="37"/>
-    </row>
-    <row r="16" spans="1:9" customFormat="1">
-      <c r="A16" s="63" t="s">
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+    </row>
+    <row r="17" spans="1:9" customFormat="1">
+      <c r="A17" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="38" t="s">
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-    </row>
-    <row r="17" spans="1:9" customFormat="1" ht="12" customHeight="1">
-      <c r="A17" s="63"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="34" t="s">
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="48"/>
+    </row>
+    <row r="18" spans="1:9" customFormat="1" ht="12" customHeight="1">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="6" t="s">
+      <c r="F18" s="37"/>
+      <c r="G18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I18" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="63"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="5"/>
-    </row>
     <row r="19" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="63"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="63"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="63"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="63"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="63"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
+      <c r="A23" s="27"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="63"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="63"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="2"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="63"/>
-      <c r="B26" s="64"/>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
+      <c r="A26" s="27"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="63"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="63"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
+      <c r="A28" s="27"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="63"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="64"/>
-      <c r="D29" s="64"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="63"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
+      <c r="A30" s="27"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="63"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
+      <c r="A31" s="27"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="63"/>
-      <c r="B32" s="64"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
+      <c r="A32" s="27"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A33" s="63"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="46" t="s">
+    <row r="33" spans="1:9" customFormat="1" ht="9" customHeight="1">
+      <c r="A33" s="27"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" customFormat="1" ht="11" customHeight="1">
+      <c r="A34" s="27"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="46"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="43"/>
-    </row>
-    <row r="34" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="48" t="s">
+      <c r="F34" s="41"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="24"/>
+    </row>
+    <row r="35" spans="1:9" customFormat="1" ht="11" customHeight="1">
+      <c r="A35" s="27"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="48"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="57"/>
-      <c r="I34" s="58"/>
-    </row>
-    <row r="35" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A35" s="63"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="59" t="s">
+      <c r="F35" s="33"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="26"/>
+    </row>
+    <row r="36" spans="1:9" customFormat="1" ht="11" customHeight="1">
+      <c r="A36" s="27"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="59"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="43"/>
-    </row>
-    <row r="36" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A36" s="63"/>
-      <c r="B36" s="64"/>
-      <c r="C36" s="64"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="48" t="s">
+      <c r="F36" s="31"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="24"/>
+    </row>
+    <row r="37" spans="1:9" customFormat="1" ht="11" customHeight="1">
+      <c r="A37" s="27"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="58"/>
-    </row>
-    <row r="37" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A37" s="63"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="59" t="s">
+      <c r="F37" s="33"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="26"/>
+    </row>
+    <row r="38" spans="1:9" customFormat="1" ht="11" customHeight="1">
+      <c r="A38" s="27"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="59"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="43"/>
-    </row>
-    <row r="38" spans="1:9" customFormat="1" ht="11" customHeight="1" thickBot="1">
-      <c r="A38" s="65"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="61" t="s">
+      <c r="F38" s="31"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="24"/>
+    </row>
+    <row r="39" spans="1:9" customFormat="1" ht="11" customHeight="1" thickBot="1">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="61"/>
-      <c r="G38" s="62"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="45"/>
-    </row>
-    <row r="39" spans="1:9" customFormat="1" ht="12" customHeight="1" thickTop="1">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="41" t="s">
+      <c r="F39" s="35"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="40"/>
+    </row>
+    <row r="40" spans="1:9" customFormat="1" ht="12" customHeight="1" thickTop="1">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-    </row>
-    <row r="40" spans="1:9" customFormat="1" ht="9" customHeight="1"/>
-    <row r="41" spans="1:9" customFormat="1"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+    </row>
+    <row r="41" spans="1:9" customFormat="1" ht="9" customHeight="1"/>
     <row r="42" spans="1:9" customFormat="1"/>
     <row r="43" spans="1:9" customFormat="1"/>
     <row r="44" spans="1:9" customFormat="1"/>
     <row r="45" spans="1:9" customFormat="1"/>
     <row r="46" spans="1:9" customFormat="1"/>
     <row r="47" spans="1:9" customFormat="1"/>
+    <row r="48" spans="1:9" customFormat="1"/>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="F5:I6"/>
-    <mergeCell ref="H33:I34"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="A16:D38"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="H37:I38"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="F14:I14"/>
+  <mergeCells count="61">
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F8:I8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="F9:I9"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="F15:I15"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="F10:I10"/>
     <mergeCell ref="A11:B11"/>
@@ -1723,18 +1748,40 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="H38:I39"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="F6:I7"/>
+    <mergeCell ref="H34:I35"/>
+    <mergeCell ref="H36:I37"/>
+    <mergeCell ref="A17:D39"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.196527777777778" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/sipil.xlsx
+++ b/public/assets/templates/maintenance/sipil.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57968CF9-0D57-47A2-80F0-4E4ACADF37C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E14F2-BA72-4B9B-A48B-9948964CA337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{CED63628-A031-421C-BEDE-C7C97718D329}"/>
   </bookViews>
@@ -30,18 +30,9 @@
     <t>FRM/EUT/01/009/019-01</t>
   </si>
   <si>
-    <t>Staff User</t>
-  </si>
-  <si>
-    <t>Diterima</t>
-  </si>
-  <si>
     <t>Staff Engineering</t>
   </si>
   <si>
-    <t>Diketahui : Miftah Hasan Fuadi</t>
-  </si>
-  <si>
     <t>Teknisi</t>
   </si>
   <si>
@@ -154,13 +145,22 @@
   </si>
   <si>
     <t xml:space="preserve">: </t>
+  </si>
+  <si>
+    <t>Diketahui : Reja Firmansyah</t>
+  </si>
+  <si>
+    <t>Supervisor Engineering</t>
+  </si>
+  <si>
+    <t>Diperiksa : Miftah Hasan Fuadi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,10 +169,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -180,23 +187,23 @@
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -204,25 +211,30 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -233,7 +245,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -264,26 +276,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -332,15 +324,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -577,224 +560,242 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{3B98E99D-BFB6-4188-ACA5-8B47D9C2B52D}"/>
     <cellStyle name="Normal_Inspection Test Plan" xfId="1" xr:uid="{3F8F5A2F-6B38-4317-BF9F-2636C1DDC7C5}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1179,7 +1180,7 @@
       <c r="A1" s="15"/>
       <c r="B1" s="16"/>
       <c r="C1" s="60" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D1" s="60"/>
       <c r="E1" s="60"/>
@@ -1192,7 +1193,7 @@
       <c r="A2" s="17"/>
       <c r="B2" s="18"/>
       <c r="C2" s="62" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D2" s="62"/>
       <c r="E2" s="62"/>
@@ -1203,75 +1204,75 @@
     </row>
     <row r="3" spans="1:9" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C3" s="67"/>
       <c r="D3" s="67"/>
       <c r="E3" s="64" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F3" s="64"/>
       <c r="G3" s="65" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H3" s="65"/>
       <c r="I3" s="66"/>
     </row>
     <row r="4" spans="1:9" customFormat="1" ht="16" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C4" s="64"/>
       <c r="D4" s="64"/>
       <c r="E4" s="64" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F4" s="64"/>
       <c r="G4" s="65" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H4" s="65"/>
       <c r="I4" s="66"/>
     </row>
     <row r="5" spans="1:9" customFormat="1" ht="16" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="68"/>
       <c r="D5" s="68"/>
       <c r="E5" s="64" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F5" s="64"/>
       <c r="G5" s="65" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H5" s="65"/>
       <c r="I5" s="66"/>
     </row>
     <row r="6" spans="1:9" customFormat="1" ht="13" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E6" s="59"/>
       <c r="F6" s="21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
@@ -1282,10 +1283,10 @@
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
@@ -1294,11 +1295,11 @@
     </row>
     <row r="8" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A8" s="51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="52"/>
       <c r="C8" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="14"/>
@@ -1309,11 +1310,11 @@
     </row>
     <row r="9" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A9" s="51" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="52"/>
       <c r="C9" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="14"/>
@@ -1324,11 +1325,11 @@
     </row>
     <row r="10" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A10" s="51" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B10" s="52"/>
       <c r="C10" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="14"/>
@@ -1339,11 +1340,11 @@
     </row>
     <row r="11" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A11" s="51" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" s="52"/>
       <c r="C11" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="14"/>
@@ -1354,11 +1355,11 @@
     </row>
     <row r="12" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A12" s="51" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" s="52"/>
       <c r="C12" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="14"/>
@@ -1369,11 +1370,11 @@
     </row>
     <row r="13" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A13" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" s="52"/>
       <c r="C13" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="14"/>
@@ -1384,11 +1385,11 @@
     </row>
     <row r="14" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A14" s="55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14" s="56"/>
       <c r="C14" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="14"/>
@@ -1410,7 +1411,7 @@
     </row>
     <row r="16" spans="1:9" s="7" customFormat="1" ht="60" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B16" s="44"/>
       <c r="C16" s="44"/>
@@ -1423,13 +1424,13 @@
     </row>
     <row r="17" spans="1:9" customFormat="1">
       <c r="A17" s="27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
       <c r="E17" s="46" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F17" s="47"/>
       <c r="G17" s="47"/>
@@ -1441,18 +1442,18 @@
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
-      <c r="E18" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="37"/>
+      <c r="E18" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="34"/>
       <c r="G18" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:9" customFormat="1" ht="9" customHeight="1">
@@ -1460,8 +1461,8 @@
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="5"/>
@@ -1471,8 +1472,8 @@
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="5"/>
@@ -1482,8 +1483,8 @@
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="5"/>
@@ -1493,8 +1494,8 @@
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
       <c r="D22" s="28"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="5"/>
@@ -1504,8 +1505,8 @@
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="5"/>
@@ -1515,8 +1516,8 @@
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="5"/>
@@ -1526,8 +1527,8 @@
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="5"/>
@@ -1537,8 +1538,8 @@
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
       <c r="D26" s="28"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="2"/>
@@ -1548,8 +1549,8 @@
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="2"/>
@@ -1559,8 +1560,8 @@
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
       <c r="D28" s="28"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="2"/>
@@ -1570,8 +1571,8 @@
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="2"/>
@@ -1581,8 +1582,8 @@
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="2"/>
@@ -1592,8 +1593,8 @@
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="2"/>
@@ -1603,8 +1604,8 @@
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="2"/>
@@ -1614,8 +1615,8 @@
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="2"/>
@@ -1625,11 +1626,11 @@
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
-      <c r="E34" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" s="41"/>
-      <c r="G34" s="42"/>
+      <c r="E34" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="38"/>
+      <c r="G34" s="39"/>
       <c r="H34" s="23"/>
       <c r="I34" s="24"/>
     </row>
@@ -1638,11 +1639,11 @@
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="33"/>
-      <c r="G35" s="34"/>
+      <c r="E35" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="25"/>
       <c r="I35" s="26"/>
     </row>
@@ -1651,11 +1652,11 @@
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
-      <c r="E36" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="32"/>
+      <c r="E36" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
       <c r="H36" s="23"/>
       <c r="I36" s="24"/>
     </row>
@@ -1664,11 +1665,11 @@
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
-      <c r="E37" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="F37" s="33"/>
-      <c r="G37" s="34"/>
+      <c r="E37" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="32"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="25"/>
       <c r="I37" s="26"/>
     </row>
@@ -1677,11 +1678,11 @@
       <c r="B38" s="28"/>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
-      <c r="E38" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="F38" s="31"/>
-      <c r="G38" s="32"/>
+      <c r="E38" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
       <c r="H38" s="23"/>
       <c r="I38" s="24"/>
     </row>
@@ -1690,13 +1691,13 @@
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
-      <c r="E39" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="35"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="40"/>
+      <c r="E39" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="31"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="37"/>
     </row>
     <row r="40" spans="1:9" customFormat="1" ht="12" customHeight="1" thickTop="1">
       <c r="A40" s="1"/>
@@ -1705,11 +1706,11 @@
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="38" t="s">
+      <c r="G40" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
     </row>
     <row r="41" spans="1:9" customFormat="1" ht="9" customHeight="1"/>
     <row r="42" spans="1:9" customFormat="1"/>
@@ -1738,6 +1739,7 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E36:G36"/>
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="F10:I10"/>
@@ -1750,8 +1752,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="A16:I16"/>
@@ -1766,22 +1766,23 @@
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E34:G34"/>
     <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="E39:G39"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="F6:I7"/>
     <mergeCell ref="H34:I35"/>
     <mergeCell ref="H36:I37"/>
     <mergeCell ref="A17:D39"/>
-    <mergeCell ref="E36:G36"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="E39:G39"/>
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.196527777777778" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/sipil.xlsx
+++ b/public/assets/templates/maintenance/sipil.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9E14F2-BA72-4B9B-A48B-9948964CA337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8BD46B-EFEF-4199-A65F-0D3DEC2D7218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{CED63628-A031-421C-BEDE-C7C97718D329}"/>
   </bookViews>
   <sheets>
-    <sheet name="SIPIL" sheetId="1" r:id="rId1"/>
+    <sheet name="SIPIL" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>FRM/EUT/01/009/019-01</t>
   </si>
@@ -51,9 +51,6 @@
     <t>MID</t>
   </si>
   <si>
-    <t>Kebutuhan Material :</t>
-  </si>
-  <si>
     <t>Tindakan Korektif :</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>Departemen</t>
   </si>
   <si>
-    <t xml:space="preserve">: </t>
-  </si>
-  <si>
     <t>Diketahui : Reja Firmansyah</t>
   </si>
   <si>
@@ -154,18 +148,31 @@
   </si>
   <si>
     <t>Diperiksa : Miftah Hasan Fuadi</t>
+  </si>
+  <si>
+    <t>List Penggantian Material :</t>
+  </si>
+  <si>
+    <t>Kebutuhan Material Agenda Selanjutnya :</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,7 +239,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="7"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -245,7 +252,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -276,36 +283,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="double">
         <color auto="1"/>
@@ -571,231 +548,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{3B98E99D-BFB6-4188-ACA5-8B47D9C2B52D}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{567CBF81-2DB4-4A5E-9D10-A1A08683651F}"/>
     <cellStyle name="Normal_Inspection Test Plan" xfId="1" xr:uid="{3F8F5A2F-6B38-4317-BF9F-2636C1DDC7C5}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -831,7 +890,7 @@
         <xdr:cNvPr id="2" name="Picture 3" descr="Logo PT.BAS">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{151C7E9F-E7D4-423A-AA7B-D6DF2F420CEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91BCA1E6-83AE-47BA-812E-8A1D5EA95586}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -848,7 +907,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="35560" y="92075"/>
-          <a:ext cx="793115" cy="238125"/>
+          <a:ext cx="1028065" cy="320675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1159,630 +1218,655 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1270B244-2998-4EEB-BD29-B19C96E8EA80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E989900-30A5-4CB5-AAF0-B48F56E399FC}">
   <dimension ref="A1:M48"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23" style="1" customWidth="1"/>
-    <col min="4" max="4" width="4.08984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.26953125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.7265625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7265625" customWidth="1"/>
-    <col min="14" max="16384" width="9.1796875" style="1"/>
+    <col min="1" max="1" width="12.54296875" style="67" customWidth="1"/>
+    <col min="2" max="2" width="3" style="67" customWidth="1"/>
+    <col min="3" max="3" width="23" style="67" customWidth="1"/>
+    <col min="4" max="5" width="5" style="67" customWidth="1"/>
+    <col min="6" max="6" width="4.7265625" style="67" customWidth="1"/>
+    <col min="7" max="7" width="18.90625" style="67" customWidth="1"/>
+    <col min="8" max="8" width="4.7265625" style="67" customWidth="1"/>
+    <col min="9" max="9" width="6" style="67" customWidth="1"/>
+    <col min="10" max="12" width="9.1796875" style="10"/>
+    <col min="13" max="13" width="10.7265625" style="10" customWidth="1"/>
+    <col min="14" max="16384" width="9.1796875" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" customFormat="1" ht="21" customHeight="1" thickTop="1">
-      <c r="A1" s="15"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="60" t="s">
+    <row r="1" spans="1:9" s="10" customFormat="1" ht="21" customHeight="1" thickTop="1">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="14"/>
+    </row>
+    <row r="3" spans="1:9" s="10" customFormat="1" ht="16" customHeight="1">
+      <c r="A3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
-    </row>
-    <row r="2" spans="1:9" customFormat="1" ht="21" customHeight="1">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="63"/>
-    </row>
-    <row r="3" spans="1:9" customFormat="1" ht="16" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" s="10" customFormat="1" ht="16" customHeight="1">
+      <c r="A4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="65"/>
-      <c r="I3" s="66"/>
-    </row>
-    <row r="4" spans="1:9" customFormat="1" ht="16" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="B4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" spans="1:9" s="10" customFormat="1" ht="13" customHeight="1">
+      <c r="A5" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64" t="s">
+      <c r="B5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="65" t="s">
+      <c r="F5" s="25"/>
+      <c r="G5" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="19"/>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" spans="1:9" s="10" customFormat="1" ht="13" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:9" s="30" customFormat="1" ht="13" customHeight="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A8" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="69"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="73"/>
+    </row>
+    <row r="9" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A9" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="69"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="73"/>
+    </row>
+    <row r="10" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A10" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="69"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="73"/>
+    </row>
+    <row r="11" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A11" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="69"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="73"/>
+    </row>
+    <row r="12" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A12" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="69"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="73"/>
+    </row>
+    <row r="13" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A13" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="69"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="73"/>
+    </row>
+    <row r="14" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A14" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="69"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="73"/>
+    </row>
+    <row r="15" spans="1:9" s="34" customFormat="1" ht="35" customHeight="1">
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="75"/>
+    </row>
+    <row r="16" spans="1:9" s="34" customFormat="1" ht="60" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" s="10" customFormat="1">
+      <c r="A17" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="44"/>
+    </row>
+    <row r="18" spans="1:9" s="10" customFormat="1" ht="12" customHeight="1">
+      <c r="A18" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="47"/>
+      <c r="D18" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="49"/>
+      <c r="G18" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A19" s="76"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="81"/>
+    </row>
+    <row r="20" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A20" s="76"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81"/>
+    </row>
+    <row r="21" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A21" s="76"/>
+      <c r="B21" s="77"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
+    </row>
+    <row r="22" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A22" s="76"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+    </row>
+    <row r="23" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A23" s="76"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="81"/>
+    </row>
+    <row r="24" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A24" s="76"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="81"/>
+    </row>
+    <row r="25" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A25" s="76"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="81"/>
+    </row>
+    <row r="26" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A26" s="76"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="82"/>
+    </row>
+    <row r="27" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A27" s="76"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="82"/>
+    </row>
+    <row r="28" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A28" s="76"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="78"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="82"/>
+    </row>
+    <row r="29" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A29" s="76"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="82"/>
+    </row>
+    <row r="30" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A30" s="76"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="82"/>
+    </row>
+    <row r="31" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A31" s="76"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="78"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="82"/>
+    </row>
+    <row r="32" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A32" s="76"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="82"/>
+    </row>
+    <row r="33" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1">
+      <c r="A33" s="76"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="78"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="82"/>
+    </row>
+    <row r="34" spans="1:9" s="10" customFormat="1" ht="11" customHeight="1">
+      <c r="A34" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="56"/>
+    </row>
+    <row r="35" spans="1:9" s="10" customFormat="1" ht="11" customHeight="1">
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="57" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="59"/>
+    </row>
+    <row r="36" spans="1:9" s="10" customFormat="1" ht="11" customHeight="1">
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="56"/>
+    </row>
+    <row r="37" spans="1:9" s="10" customFormat="1" ht="11" customHeight="1">
+      <c r="A37" s="51"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="62"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="59"/>
+    </row>
+    <row r="38" spans="1:9" s="10" customFormat="1" ht="11" customHeight="1">
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="56"/>
+    </row>
+    <row r="39" spans="1:9" s="10" customFormat="1" ht="11" customHeight="1" thickBot="1">
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="65"/>
-      <c r="I4" s="66"/>
-    </row>
-    <row r="5" spans="1:9" customFormat="1" ht="16" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="66"/>
-    </row>
-    <row r="6" spans="1:9" customFormat="1" ht="13" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-    </row>
-    <row r="7" spans="1:9" s="11" customFormat="1" ht="13" customHeight="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22"/>
-    </row>
-    <row r="8" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A8" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="54"/>
-    </row>
-    <row r="9" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A9" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="52"/>
-      <c r="C9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="54"/>
-    </row>
-    <row r="10" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A10" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="54"/>
-    </row>
-    <row r="11" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A11" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="52"/>
-      <c r="C11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="54"/>
-    </row>
-    <row r="12" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A12" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="54"/>
-    </row>
-    <row r="13" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A13" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="54"/>
-    </row>
-    <row r="14" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A14" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="54"/>
-    </row>
-    <row r="15" spans="1:9" s="7" customFormat="1" ht="35" customHeight="1">
-      <c r="A15" s="57"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-    </row>
-    <row r="16" spans="1:9" s="7" customFormat="1" ht="60" customHeight="1">
-      <c r="A16" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45"/>
-    </row>
-    <row r="17" spans="1:9" customFormat="1">
-      <c r="A17" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
-    </row>
-    <row r="18" spans="1:9" customFormat="1" ht="12" customHeight="1">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="27"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="27"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="27"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="27"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="27"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="27"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="27"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="27"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="27"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A34" s="27"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="38"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="24"/>
-    </row>
-    <row r="35" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A35" s="27"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" s="32"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="26"/>
-    </row>
-    <row r="36" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A36" s="27"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="69" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="24"/>
-    </row>
-    <row r="37" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A37" s="27"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="32"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="26"/>
-    </row>
-    <row r="38" spans="1:9" customFormat="1" ht="11" customHeight="1">
-      <c r="A38" s="27"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="24"/>
-    </row>
-    <row r="39" spans="1:9" customFormat="1" ht="11" customHeight="1" thickBot="1">
-      <c r="A39" s="29"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="31"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="37"/>
-    </row>
-    <row r="40" spans="1:9" customFormat="1" ht="12" customHeight="1" thickTop="1">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="35" t="s">
+      <c r="F39" s="62"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="66"/>
+    </row>
+    <row r="40" spans="1:9" s="10" customFormat="1" ht="12" customHeight="1" thickTop="1">
+      <c r="A40" s="67"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-    </row>
-    <row r="41" spans="1:9" customFormat="1" ht="9" customHeight="1"/>
-    <row r="42" spans="1:9" customFormat="1"/>
-    <row r="43" spans="1:9" customFormat="1"/>
-    <row r="44" spans="1:9" customFormat="1"/>
-    <row r="45" spans="1:9" customFormat="1"/>
-    <row r="46" spans="1:9" customFormat="1"/>
-    <row r="47" spans="1:9" customFormat="1"/>
-    <row r="48" spans="1:9" customFormat="1"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="68"/>
+    </row>
+    <row r="41" spans="1:9" s="10" customFormat="1" ht="9" customHeight="1"/>
+    <row r="42" spans="1:9" s="10" customFormat="1"/>
+    <row r="43" spans="1:9" s="10" customFormat="1"/>
+    <row r="44" spans="1:9" s="10" customFormat="1"/>
+    <row r="45" spans="1:9" s="10" customFormat="1"/>
+    <row r="46" spans="1:9" s="10" customFormat="1"/>
+    <row r="47" spans="1:9" s="10" customFormat="1"/>
+    <row r="48" spans="1:9" s="10" customFormat="1"/>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="C6:C7"/>
+  <mergeCells count="78">
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="A34:D39"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="H34:I35"/>
+    <mergeCell ref="E35:G35"/>
     <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H36:I37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H38:I39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="F15:I15"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="E18:F18"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="F14:I14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="H38:I39"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:I7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="F6:I7"/>
-    <mergeCell ref="H34:I35"/>
-    <mergeCell ref="H36:I37"/>
-    <mergeCell ref="A17:D39"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.196527777777778" bottom="0" header="0" footer="0"/>
